--- a/artfynd/A 1791-2022 artfynd.xlsx
+++ b/artfynd/A 1791-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1791-2022 artfynd.xlsx
+++ b/artfynd/A 1791-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57194946</v>
+        <v>62085869</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222295</v>
+        <v>220204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502014.5854199286</v>
+        <v>502015</v>
       </c>
       <c r="R2" t="n">
-        <v>6524414.576750279</v>
+        <v>6524415</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1978-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1978-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62085869</v>
+        <v>62124237</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>220228</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502014.5854199286</v>
+        <v>502015</v>
       </c>
       <c r="R3" t="n">
-        <v>6524414.576750279</v>
+        <v>6524415</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +840,9 @@
           <t>1978-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1978-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +869,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62088790</v>
+        <v>62431548</v>
       </c>
       <c r="B4" t="n">
-        <v>103088</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221101</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502014.5854199286</v>
+        <v>502015</v>
       </c>
       <c r="R4" t="n">
-        <v>6524414.576750279</v>
+        <v>6524415</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,19 +937,9 @@
           <t>1978-07-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1978-07-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,32 +966,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62124237</v>
+        <v>62088790</v>
       </c>
       <c r="B5" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220228</v>
+        <v>221101</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502014.5854199286</v>
+        <v>502015</v>
       </c>
       <c r="R5" t="n">
-        <v>6524414.576750279</v>
+        <v>6524415</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1084,19 +1034,9 @@
           <t>1978-07-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1978-07-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62361960</v>
+        <v>62361959</v>
       </c>
       <c r="B6" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nyhyttan 6650/5550, Nrk</t>
+          <t>Nyhyttan 6550/5450, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502014.5854199286</v>
+        <v>501916</v>
       </c>
       <c r="R6" t="n">
-        <v>6524414.576750279</v>
+        <v>6524313</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1193,22 +1128,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1978-07-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1978-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-08-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,6 +1149,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Björkdominerad hage</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1235,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62361959</v>
+        <v>62361960</v>
       </c>
       <c r="B7" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,14 +1201,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nyhyttan 6550/5450, Nrk</t>
+          <t>Nyhyttan 6650/5550, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501915.6589611266</v>
+        <v>502015</v>
       </c>
       <c r="R7" t="n">
-        <v>6524313.140021061</v>
+        <v>6524415</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1305,27 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1978-07-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
+          <t>1978-07-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,11 +1251,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Björkdominerad hage</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1357,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62431548</v>
+        <v>62477659</v>
       </c>
       <c r="B8" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502014.5854199286</v>
+        <v>502015</v>
       </c>
       <c r="R8" t="n">
-        <v>6524414.576750279</v>
+        <v>6524415</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1430,19 +1335,14 @@
           <t>1978-07-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1978-07-25</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,15 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62477659</v>
+        <v>57194946</v>
       </c>
       <c r="B9" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221317</v>
+        <v>222295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502014.5854199286</v>
+        <v>502015</v>
       </c>
       <c r="R9" t="n">
-        <v>6524414.576750279</v>
+        <v>6524415</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1542,24 +1437,9 @@
           <t>1978-07-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1978-07-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 1791-2022 artfynd.xlsx
+++ b/artfynd/A 1791-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62085869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62124237</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62431548</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62088790</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62361959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62361960</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62477659</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,8 +1503,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57194946</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>